--- a/CT 050.xlsx
+++ b/CT 050.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <r>
       <rPr>
@@ -72,9 +72,6 @@
     <t>TRẠNG THÁI HOẠT ĐỘNG</t>
   </si>
   <si>
-    <t>Bình thường</t>
-  </si>
-  <si>
     <t>NHÂN VIÊN QUẢN LÝ</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>GOOGLE MAP</t>
   </si>
   <si>
-    <t>QR</t>
-  </si>
-  <si>
     <t>NGÀY KIỂM TRA</t>
   </si>
   <si>
@@ -123,17 +117,6 @@
     <t>6 cửa</t>
   </si>
   <si>
-    <t>B = 10m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Cống vệ sinh tốt
-- Mốc ranh còn đủ: 5/5 trụ
-</t>
-  </si>
-  <si>
-    <t>Kiểm tra lần cuối vào ngày 27/2026</t>
-  </si>
-  <si>
     <t>GIOI THIEU CONG TRINH.pdf</t>
   </si>
   <si>
@@ -141,6 +124,21 @@
   </si>
   <si>
     <t>src="https://www.google.com/maps/embed?pb=!1m17!1m12!1m3!1d2093.944628074404!2d106.45969343887784!3d10.068608523530434!2m3!1f0!2f0!3f0!3m2!1i1024!2i768!4f13.1!3m2!1m1!2zMTDCsDA0JzA2LjMiTiAxMDbCsDI3JzMwLjYiRQ!5e1!3m2!1svi!2s!4v1777617304323!5m2!1svi!2s" width="600" height="450" style="border:0;" allowfullscreen="" loading="lazy" referrerpolicy="no-referrer-when-downgrade"</t>
+  </si>
+  <si>
+    <t>LINK ƯEB</t>
+  </si>
+  <si>
+    <t>https://lehuy-ops.github.io/Son-Doc-2/</t>
+  </si>
+  <si>
+    <t>……….</t>
+  </si>
+  <si>
+    <t>Bề rộng 1 cửa B = 10m</t>
+  </si>
+  <si>
+    <t>Đang hoạt động</t>
   </si>
 </sst>
 </file>
@@ -281,7 +279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -345,15 +343,9 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -362,6 +354,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -672,66 +667,70 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="31.1640625" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="21.83203125" customWidth="1"/>
-    <col min="12" max="13" width="34.33203125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="45.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="34.33203125" style="8" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" customWidth="1"/>
+    <col min="12" max="12" width="29.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.1640625" style="8" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="21.33203125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="34.33203125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
       <c r="O1" s="10"/>
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="O2" s="11"/>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
     </row>
     <row r="3" spans="1:18" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>6</v>
@@ -743,7 +742,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
@@ -756,60 +755,60 @@
         <v>7</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="O3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="Q3" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="189" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>50</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F4" s="17">
         <v>60</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H4" s="19">
         <v>2013</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J4" s="3" t="str">
         <f t="shared" ref="J4" si="0">IF(F4&gt;=20,"Cống lớn",IF(AND(F4&gt;=3,F4&lt;20),"Cống vừa","Cống nhỏ"))</f>
@@ -820,24 +819,26 @@
         <v>50</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="22" t="s">
+      <c r="Q4" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="R4" s="21"/>
     </row>
     <row r="5" spans="1:18" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N5" s="14"/>

--- a/CT 050.xlsx
+++ b/CT 050.xlsx
@@ -346,17 +346,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -687,43 +687,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
       <c r="O1" s="10"/>
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
       <c r="O2" s="11"/>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
@@ -827,7 +827,7 @@
       <c r="N4" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="24" t="s">
+      <c r="O4" s="22" t="s">
         <v>23</v>
       </c>
       <c r="P4" s="21" t="s">
@@ -836,7 +836,7 @@
       <c r="Q4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="25" t="s">
+      <c r="R4" s="23" t="s">
         <v>27</v>
       </c>
     </row>
@@ -857,8 +857,9 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O4" r:id="rId1"/>
+    <hyperlink ref="R4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.92" right="0.70866141732283472" top="0.35433070866141736" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
--- a/CT 050.xlsx
+++ b/CT 050.xlsx
@@ -117,9 +117,6 @@
     <t>6 cửa</t>
   </si>
   <si>
-    <t>GIOI THIEU CONG TRINH.pdf</t>
-  </si>
-  <si>
     <t>Đoàn Văn Phường</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>Đang hoạt động</t>
+  </si>
+  <si>
+    <t>GIOT THIEU CONG TRINH.pdf</t>
   </si>
 </sst>
 </file>
@@ -680,7 +680,7 @@
     <col min="12" max="12" width="29.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30.1640625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" style="8" customWidth="1"/>
+    <col min="15" max="15" width="34.5" style="8" customWidth="1"/>
     <col min="16" max="16" width="21.33203125" style="8" customWidth="1"/>
     <col min="17" max="17" width="34.33203125" style="8" customWidth="1"/>
     <col min="18" max="18" width="22.5" customWidth="1"/>
@@ -779,7 +779,7 @@
         <v>16</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -796,7 +796,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" s="17">
         <v>60</v>
@@ -808,7 +808,7 @@
         <v>2013</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J4" s="3" t="str">
         <f t="shared" ref="J4" si="0">IF(F4&gt;=20,"Cống lớn",IF(AND(F4&gt;=3,F4&lt;20),"Cống vừa","Cống nhỏ"))</f>
@@ -819,25 +819,25 @@
         <v>50</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="N4" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" s="22" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P4" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -856,8 +856,8 @@
     <mergeCell ref="A2:N2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O4" r:id="rId1"/>
-    <hyperlink ref="R4" r:id="rId2"/>
+    <hyperlink ref="R4" r:id="rId1"/>
+    <hyperlink ref="O4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.92" right="0.70866141732283472" top="0.35433070866141736" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId3"/>
